--- a/cet4/result/33_双生姐妹_豪门千金的逆袭计划/33_双生姐妹_豪门千金的逆袭计划_学习版.xlsx
+++ b/cet4/result/33_双生姐妹_豪门千金的逆袭计划/33_双生姐妹_豪门千金的逆袭计划_学习版.xlsx
@@ -397,969 +397,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D52"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>headquarters</v>
       </c>
       <c r="B2" t="str">
-        <v>headquarters</v>
+        <v>/ˈhedkwɔːrtərz/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>总部</v>
       </c>
-      <c r="D2" t="str">
-        <v>headquarters(总部)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>twin</v>
       </c>
       <c r="B3" t="str">
-        <v>twin</v>
+        <v>/twɪn/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>双胞胎</v>
       </c>
-      <c r="D3" t="str">
-        <v>twin(双胞胎)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>resemble</v>
       </c>
       <c r="B4" t="str">
-        <v>resemble</v>
+        <v>/rɪˈzembl/</v>
       </c>
       <c r="C4" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D4" t="str">
         <v>相似</v>
       </c>
-      <c r="D4" t="str">
-        <v>resemble(相似)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>careful</v>
       </c>
       <c r="B5" t="str">
-        <v>careful</v>
+        <v>/ˈkerfl/</v>
       </c>
       <c r="C5" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>谨慎</v>
       </c>
-      <c r="D5" t="str">
-        <v>careful(谨慎)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>dynamic</v>
       </c>
       <c r="B6" t="str">
-        <v>dynamic</v>
+        <v>/daɪˈnæmɪk/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>有活力的</v>
       </c>
-      <c r="D6" t="str">
-        <v>dynamic(有活力的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>thirty</v>
       </c>
       <c r="B7" t="str">
-        <v>thirty</v>
+        <v>/ˈθɜːrti/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D7" t="str">
         <v>三十</v>
       </c>
-      <c r="D7" t="str">
-        <v>thirty(三十)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>board</v>
       </c>
       <c r="B8" t="str">
-        <v>board</v>
+        <v>/bɔːrd/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>董事会</v>
       </c>
-      <c r="D8" t="str">
-        <v>board(董事会)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>core</v>
       </c>
       <c r="B9" t="str">
-        <v>core</v>
+        <v>/kɔːr/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D9" t="str">
         <v>核心</v>
       </c>
-      <c r="D9" t="str">
-        <v>core(核心)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>impossible</v>
       </c>
       <c r="B10" t="str">
-        <v>impossible</v>
+        <v>/ɪmˈpɑːsəbl/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>不可能</v>
       </c>
-      <c r="D10" t="str">
-        <v>impossible(不可能)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>merely</v>
       </c>
       <c r="B11" t="str">
-        <v>merely</v>
+        <v>/ˈmɪrli/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D11" t="str">
         <v>仅仅</v>
       </c>
-      <c r="D11" t="str">
-        <v>merely(仅仅)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>valid</v>
       </c>
       <c r="B12" t="str">
-        <v>valid</v>
+        <v>/ˈvælɪd/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>有效的</v>
       </c>
-      <c r="D12" t="str">
-        <v>valid(有效的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>region</v>
       </c>
       <c r="B13" t="str">
-        <v>region</v>
+        <v>/ˈriːdʒən/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>地区</v>
       </c>
-      <c r="D13" t="str">
-        <v>region(地区)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>eight</v>
       </c>
       <c r="B14" t="str">
-        <v>eight</v>
+        <v>/eɪt/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D14" t="str">
         <v>八</v>
       </c>
-      <c r="D14" t="str">
-        <v>eight(八)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>month</v>
       </c>
       <c r="B15" t="str">
-        <v>month</v>
+        <v>/mʌnθ/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>月</v>
       </c>
-      <c r="D15" t="str">
-        <v>month(月)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>cloth</v>
       </c>
       <c r="B16" t="str">
-        <v>cloth</v>
+        <v>/klɔːθ/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>布料</v>
       </c>
-      <c r="D16" t="str">
-        <v>cloth(布料)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>nest</v>
       </c>
       <c r="B17" t="str">
-        <v>nest</v>
+        <v>/nest/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D17" t="str">
         <v>巢</v>
       </c>
-      <c r="D17" t="str">
-        <v>nest(巢)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>fountain</v>
       </c>
       <c r="B18" t="str">
-        <v>fountain</v>
+        <v>/ˈfaʊntn/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>喷泉</v>
       </c>
-      <c r="D18" t="str">
-        <v>fountain(喷泉)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>Portugal</v>
       </c>
       <c r="B19" t="str">
-        <v>Portugal</v>
+        <v>/ˈpɔːrtʃʊɡl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>葡萄牙</v>
       </c>
-      <c r="D19" t="str">
-        <v>Portugal(葡萄牙)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>diamond</v>
       </c>
       <c r="B20" t="str">
-        <v>diamond</v>
+        <v>/ˈdaɪmənd/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>钻石</v>
       </c>
-      <c r="D20" t="str">
-        <v>diamond(钻石)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>brilliant</v>
       </c>
       <c r="B21" t="str">
-        <v>brilliant</v>
+        <v>/ˈbrɪliənt/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>杰出的</v>
       </c>
-      <c r="D21" t="str">
-        <v>brilliant(杰出的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>absent</v>
       </c>
       <c r="B22" t="str">
-        <v>absent</v>
+        <v>/ˈæbsənt/</v>
       </c>
       <c r="C22" t="str">
+        <v>vt./adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>缺席</v>
       </c>
-      <c r="D22" t="str">
-        <v>absent(缺席)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>appointment</v>
       </c>
       <c r="B23" t="str">
-        <v>appointment</v>
+        <v>/əˈpɔɪntmənt/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>约定</v>
       </c>
-      <c r="D23" t="str">
-        <v>appointment(约定)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>output</v>
       </c>
       <c r="B24" t="str">
-        <v>output</v>
+        <v>/ˈaʊtpʊt/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D24" t="str">
         <v>产量</v>
       </c>
-      <c r="D24" t="str">
-        <v>output(产量)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>meal</v>
       </c>
       <c r="B25" t="str">
-        <v>Portugal</v>
+        <v>/miːl/</v>
       </c>
       <c r="C25" t="str">
-        <v>葡萄牙</v>
+        <v>n./vi.</v>
       </c>
       <c r="D25" t="str">
-        <v>Portugal(葡萄牙)📢</v>
+        <v>餐</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>carrot</v>
       </c>
       <c r="B26" t="str">
-        <v>meal</v>
+        <v>/ˈkærət/</v>
       </c>
       <c r="C26" t="str">
-        <v>餐</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>meal(餐)📢</v>
+        <v>胡萝卜</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>brown</v>
       </c>
       <c r="B27" t="str">
-        <v>carrot</v>
+        <v>/braʊn/</v>
       </c>
       <c r="C27" t="str">
-        <v>胡萝卜</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>carrot(胡萝卜)📢</v>
+        <v>棕色</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>physicist</v>
       </c>
       <c r="B28" t="str">
-        <v>brown</v>
+        <v>/ˈfɪzɪsɪst/</v>
       </c>
       <c r="C28" t="str">
-        <v>棕色</v>
+        <v>n.</v>
       </c>
       <c r="D28" t="str">
-        <v>brown(棕色)📢</v>
+        <v>物理学家</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>variation</v>
       </c>
       <c r="B29" t="str">
-        <v>physicist</v>
+        <v>/ˌveriˈeɪʃn/</v>
       </c>
       <c r="C29" t="str">
-        <v>物理学家</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>physicist(物理学家)📢</v>
+        <v>变化</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>specify</v>
       </c>
       <c r="B30" t="str">
-        <v>variation</v>
+        <v>/ˈspesɪfaɪ/</v>
       </c>
       <c r="C30" t="str">
-        <v>变化</v>
+        <v>vt.</v>
       </c>
       <c r="D30" t="str">
-        <v>variation(变化)📢</v>
+        <v>具体说明</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>loan</v>
       </c>
       <c r="B31" t="str">
-        <v>specify</v>
+        <v>/loʊn/</v>
       </c>
       <c r="C31" t="str">
-        <v>具体说明</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>specify(具体说明)📢</v>
+        <v>贷款</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>borrow</v>
       </c>
       <c r="B32" t="str">
-        <v>loan</v>
+        <v>/ˈbɔːroʊ/</v>
       </c>
       <c r="C32" t="str">
-        <v>贷款</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>loan(贷款)📢</v>
+        <v>借</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>exchange</v>
       </c>
       <c r="B33" t="str">
-        <v>borrow</v>
+        <v>/ɪksˈtʃeɪndʒ/</v>
       </c>
       <c r="C33" t="str">
-        <v>借</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>borrow(借)📢</v>
+        <v>交换</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>account</v>
       </c>
       <c r="B34" t="str">
-        <v>exchange</v>
+        <v>/əˈkaʊnt/</v>
       </c>
       <c r="C34" t="str">
-        <v>交换</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>exchange(交换)📢</v>
+        <v>账户</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>confident</v>
       </c>
       <c r="B35" t="str">
-        <v>account</v>
+        <v>/ˈkɑːnfɪdənt/</v>
       </c>
       <c r="C35" t="str">
-        <v>账户</v>
+        <v>adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>account(账户)📢</v>
+        <v>自信的</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>donkey</v>
       </c>
       <c r="B36" t="str">
-        <v>confident</v>
+        <v>/ˈdɑːŋki/</v>
       </c>
       <c r="C36" t="str">
-        <v>自信的</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>confident(自信的)📢</v>
+        <v>驴子</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>justice</v>
       </c>
       <c r="B37" t="str">
-        <v>donkey</v>
+        <v>/ˈdʒʌstɪs/</v>
       </c>
       <c r="C37" t="str">
-        <v>驴子</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>donkey(驴子)📢</v>
+        <v>公正</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>message</v>
       </c>
       <c r="B38" t="str">
-        <v>month</v>
+        <v>/ˈmesɪdʒ/</v>
       </c>
       <c r="C38" t="str">
-        <v>月</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>month(月)📢</v>
+        <v>消息</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>stiff</v>
       </c>
       <c r="B39" t="str">
-        <v>justice</v>
+        <v>/stɪf/</v>
       </c>
       <c r="C39" t="str">
-        <v>公正</v>
+        <v>adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>justice(公正)📢</v>
+        <v>坚硬的</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>escape</v>
       </c>
       <c r="B40" t="str">
-        <v>message</v>
+        <v>/ɪˈskeɪp/</v>
       </c>
       <c r="C40" t="str">
-        <v>消息</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>message(消息)📢</v>
+        <v>逃离</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>gradual</v>
       </c>
       <c r="B41" t="str">
-        <v>stiff</v>
+        <v>/ˈɡrædʒuəl/</v>
       </c>
       <c r="C41" t="str">
-        <v>坚硬的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>stiff(坚硬的)📢</v>
+        <v>逐渐的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>leaf</v>
       </c>
       <c r="B42" t="str">
-        <v>escape</v>
+        <v>/liːf/</v>
       </c>
       <c r="C42" t="str">
-        <v>逃离</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>escape(逃离)📢</v>
+        <v>叶子</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>side</v>
       </c>
       <c r="B43" t="str">
-        <v>eight</v>
+        <v>/saɪd/</v>
       </c>
       <c r="C43" t="str">
-        <v>八</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>eight(八)📢</v>
+        <v>旁边</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>stick</v>
       </c>
       <c r="B44" t="str">
-        <v>gradual</v>
+        <v>/stɪk/</v>
       </c>
       <c r="C44" t="str">
-        <v>逐渐的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>gradual(逐渐的)📢</v>
+        <v>树枝</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>cake</v>
       </c>
       <c r="B45" t="str">
-        <v>leaf</v>
+        <v>/keɪk/</v>
       </c>
       <c r="C45" t="str">
-        <v>叶子</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>leaf(叶子)📢</v>
+        <v>蛋糕</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>fry</v>
       </c>
       <c r="B46" t="str">
-        <v>side</v>
+        <v>/fraɪ/</v>
       </c>
       <c r="C46" t="str">
-        <v>旁边</v>
+        <v>n./v.</v>
       </c>
       <c r="D46" t="str">
-        <v>side(旁边)📢</v>
+        <v>油炸</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>thrive</v>
       </c>
       <c r="B47" t="str">
-        <v>stick</v>
+        <v>/θraɪv/</v>
       </c>
       <c r="C47" t="str">
-        <v>树枝</v>
+        <v>vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>stick(树枝)📢</v>
+        <v>繁荣</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>swarm</v>
       </c>
       <c r="B48" t="str">
-        <v>cake</v>
+        <v>/swɔːrm/</v>
       </c>
       <c r="C48" t="str">
-        <v>蛋糕</v>
+        <v>n./v.</v>
       </c>
       <c r="D48" t="str">
-        <v>cake(蛋糕)📢</v>
+        <v>一大群</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>thirsty</v>
       </c>
       <c r="B49" t="str">
-        <v>fry</v>
+        <v>/ˈθɜːrsti/</v>
       </c>
       <c r="C49" t="str">
-        <v>油炸</v>
+        <v>adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>fry(油炸)📢</v>
+        <v>口渴的</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>beside</v>
       </c>
       <c r="B50" t="str">
-        <v>thrive</v>
+        <v>/bɪˈsaɪd/</v>
       </c>
       <c r="C50" t="str">
-        <v>繁荣</v>
+        <v>v./adv./prep.</v>
       </c>
       <c r="D50" t="str">
-        <v>thrive(繁荣)📢</v>
+        <v>在旁边</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>restrict</v>
       </c>
       <c r="B51" t="str">
-        <v>swarm</v>
+        <v>/rɪˈstrɪkt/</v>
       </c>
       <c r="C51" t="str">
-        <v>一大群</v>
+        <v>vt.</v>
       </c>
       <c r="D51" t="str">
-        <v>swarm(一大群)📢</v>
+        <v>限制</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>refusal</v>
       </c>
       <c r="B52" t="str">
-        <v>output</v>
+        <v>/rɪˈfjuːzl/</v>
       </c>
       <c r="C52" t="str">
-        <v>产量</v>
+        <v>n.</v>
       </c>
       <c r="D52" t="str">
-        <v>output(产量)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>diamond</v>
-      </c>
-      <c r="C53" t="str">
-        <v>钻石</v>
-      </c>
-      <c r="D53" t="str">
-        <v>diamond(钻石)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>thirsty</v>
-      </c>
-      <c r="C54" t="str">
-        <v>口渴的</v>
-      </c>
-      <c r="D54" t="str">
-        <v>thirsty(口渴的)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>stick</v>
-      </c>
-      <c r="C55" t="str">
-        <v>坚持</v>
-      </c>
-      <c r="D55" t="str">
-        <v>stick(坚持)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>side</v>
-      </c>
-      <c r="C56" t="str">
-        <v>方面</v>
-      </c>
-      <c r="D56" t="str">
-        <v>side(方面)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>brilliant</v>
-      </c>
-      <c r="C57" t="str">
-        <v>杰出的</v>
-      </c>
-      <c r="D57" t="str">
-        <v>brilliant(杰出的)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>dynamic</v>
-      </c>
-      <c r="C58" t="str">
-        <v>动态的</v>
-      </c>
-      <c r="D58" t="str">
-        <v>dynamic(动态的)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>variation</v>
-      </c>
-      <c r="C59" t="str">
-        <v>变化</v>
-      </c>
-      <c r="D59" t="str">
-        <v>variation(变化)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>beside</v>
-      </c>
-      <c r="C60" t="str">
-        <v>在旁边</v>
-      </c>
-      <c r="D60" t="str">
-        <v>beside(在旁边)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>restrict</v>
-      </c>
-      <c r="C61" t="str">
-        <v>限制</v>
-      </c>
-      <c r="D61" t="str">
-        <v>restrict(限制)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>escape</v>
-      </c>
-      <c r="C62" t="str">
-        <v>突破</v>
-      </c>
-      <c r="D62" t="str">
-        <v>escape(突破)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>exchange</v>
-      </c>
-      <c r="C63" t="str">
-        <v>交换</v>
-      </c>
-      <c r="D63" t="str">
-        <v>exchange(交换)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>valid</v>
-      </c>
-      <c r="C64" t="str">
-        <v>有效的</v>
-      </c>
-      <c r="D64" t="str">
-        <v>valid(有效的)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>brilliant</v>
-      </c>
-      <c r="C65" t="str">
-        <v>杰出的</v>
-      </c>
-      <c r="D65" t="str">
-        <v>brilliant(杰出的)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>beside</v>
-      </c>
-      <c r="C66" t="str">
-        <v>在一起</v>
-      </c>
-      <c r="D66" t="str">
-        <v>beside(在一起)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>refusal</v>
-      </c>
-      <c r="C67" t="str">
         <v>拒绝</v>
-      </c>
-      <c r="D67" t="str">
-        <v>refusal(拒绝)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>beside</v>
-      </c>
-      <c r="C68" t="str">
-        <v>在旁边</v>
-      </c>
-      <c r="D68" t="str">
-        <v>beside(在旁边)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>